--- a/sheets/조재수대금교본/검수/어부의 노래.xlsx
+++ b/sheets/조재수대금교본/검수/어부의 노래.xlsx
@@ -3542,11 +3542,7 @@
     </row>
     <row r="5" ht="90.2" customHeight="true">
       <c r="A5" s="0"/>
-      <c r="B5" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="B5" s="21"/>
       <c r="C5" s="24"/>
       <c r="D5" s="21" t="inlineStr">
         <is>
@@ -3556,11 +3552,7 @@
         </is>
       </c>
       <c r="E5" s="24"/>
-      <c r="F5" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="F5" s="21"/>
       <c r="G5" s="24"/>
       <c r="H5" s="21" t="inlineStr">
         <is>
@@ -3570,11 +3562,7 @@
         </is>
       </c>
       <c r="I5" s="24"/>
-      <c r="J5" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="J5" s="21"/>
       <c r="K5" s="24"/>
       <c r="L5" s="21" t="inlineStr">
         <is>
@@ -3584,11 +3572,7 @@
         </is>
       </c>
       <c r="M5" s="24"/>
-      <c r="N5" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="N5" s="21"/>
       <c r="O5" s="24"/>
       <c r="P5" s="21" t="inlineStr">
         <is>
@@ -3762,19 +3746,11 @@
         </is>
       </c>
       <c r="C9" s="22"/>
-      <c r="D9" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="D9" s="21"/>
       <c r="E9" s="22"/>
       <c r="F9" s="21"/>
       <c r="G9" s="22"/>
-      <c r="H9" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="H9" s="21"/>
       <c r="I9" s="22"/>
       <c r="J9" s="21" t="inlineStr">
         <is>
@@ -3784,11 +3760,7 @@
         </is>
       </c>
       <c r="K9" s="22"/>
-      <c r="L9" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="L9" s="21"/>
       <c r="M9" s="22"/>
       <c r="N9" s="21" t="inlineStr">
         <is>
@@ -3798,11 +3770,7 @@
         </is>
       </c>
       <c r="O9" s="22"/>
-      <c r="P9" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="P9" s="21"/>
       <c r="Q9" s="22"/>
     </row>
     <row r="10" ht="90.2" customHeight="true">
@@ -3972,11 +3940,7 @@
       <c r="C13" s="23"/>
       <c r="D13" s="21"/>
       <c r="E13" s="23"/>
-      <c r="F13" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="F13" s="21"/>
       <c r="G13" s="23"/>
       <c r="H13" s="21" t="inlineStr">
         <is>
@@ -3986,11 +3950,7 @@
         </is>
       </c>
       <c r="I13" s="23"/>
-      <c r="J13" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="J13" s="21"/>
       <c r="K13" s="23"/>
       <c r="L13" s="21" t="inlineStr">
         <is>
@@ -4000,11 +3960,7 @@
         </is>
       </c>
       <c r="M13" s="23"/>
-      <c r="N13" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="N13" s="21"/>
       <c r="O13" s="23"/>
       <c r="P13" s="21" t="inlineStr">
         <is>

--- a/sheets/조재수대금교본/검수/어부의 노래.xlsx
+++ b/sheets/조재수대금교본/검수/어부의 노래.xlsx
@@ -3408,28 +3408,28 @@
   </sheetPr>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
+    <col min="2" max="2" width="10.71" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="9" customWidth="1"/>
+    <col min="4" max="4" width="10.71" customWidth="1"/>
     <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="9" customWidth="1"/>
+    <col min="6" max="6" width="10.71" customWidth="1"/>
     <col min="7" max="7" width="6" customWidth="1"/>
-    <col min="8" max="8" width="9" customWidth="1"/>
+    <col min="8" max="8" width="10.71" customWidth="1"/>
     <col min="9" max="9" width="6" customWidth="1"/>
-    <col min="10" max="10" width="9" customWidth="1"/>
+    <col min="10" max="10" width="10.71" customWidth="1"/>
     <col min="11" max="11" width="6" customWidth="1"/>
-    <col min="12" max="12" width="9" customWidth="1"/>
+    <col min="12" max="12" width="10.71" customWidth="1"/>
     <col min="13" max="13" width="6" customWidth="1"/>
-    <col min="14" max="14" width="9" customWidth="1"/>
+    <col min="14" max="14" width="10.71" customWidth="1"/>
     <col min="15" max="15" width="6" customWidth="1"/>
-    <col min="16" max="16" width="9" customWidth="1"/>
+    <col min="16" max="16" width="10.71" customWidth="1"/>
     <col min="17" max="17" width="6" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="6.0" customHeight="true">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="60.61" customHeight="true">
+    <row r="2" ht="64.52" customHeight="true">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -3452,7 +3452,7 @@
       <c r="P2" s="20"/>
       <c r="Q2" s="20"/>
     </row>
-    <row r="3" ht="90.2" customHeight="true">
+    <row r="3" ht="96.05" customHeight="true">
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
@@ -3503,7 +3503,7 @@
       </c>
       <c r="Q3" s="22"/>
     </row>
-    <row r="4" ht="90.2" customHeight="true">
+    <row r="4" ht="96.05" customHeight="true">
       <c r="A4" s="0"/>
       <c r="B4" s="21"/>
       <c r="C4" s="23"/>
@@ -3540,7 +3540,7 @@
       </c>
       <c r="Q4" s="23"/>
     </row>
-    <row r="5" ht="90.2" customHeight="true">
+    <row r="5" ht="96.05" customHeight="true">
       <c r="A5" s="0"/>
       <c r="B5" s="21"/>
       <c r="C5" s="24"/>
@@ -3583,7 +3583,7 @@
       </c>
       <c r="Q5" s="24"/>
     </row>
-    <row r="6" ht="90.2" customHeight="true">
+    <row r="6" ht="96.05" customHeight="true">
       <c r="A6" s="0"/>
       <c r="B6" s="21" t="inlineStr">
         <is>
@@ -3648,7 +3648,7 @@
       </c>
       <c r="Q6" s="22"/>
     </row>
-    <row r="7" ht="90.2" customHeight="true">
+    <row r="7" ht="96.05" customHeight="true">
       <c r="A7" s="0"/>
       <c r="B7" s="21" t="inlineStr">
         <is>
@@ -3699,7 +3699,7 @@
       </c>
       <c r="Q7" s="23"/>
     </row>
-    <row r="8" ht="90.2" customHeight="true">
+    <row r="8" ht="96.05" customHeight="true">
       <c r="A8" s="0"/>
       <c r="B8" s="21" t="inlineStr">
         <is>
@@ -3736,7 +3736,7 @@
       <c r="P8" s="21"/>
       <c r="Q8" s="24"/>
     </row>
-    <row r="9" ht="90.2" customHeight="true">
+    <row r="9" ht="96.05" customHeight="true">
       <c r="A9" s="0"/>
       <c r="B9" s="21" t="inlineStr">
         <is>
@@ -3773,7 +3773,7 @@
       <c r="P9" s="21"/>
       <c r="Q9" s="22"/>
     </row>
-    <row r="10" ht="90.2" customHeight="true">
+    <row r="10" ht="96.05" customHeight="true">
       <c r="A10" s="0"/>
       <c r="B10" s="21" t="inlineStr">
         <is>
@@ -3832,7 +3832,7 @@
       </c>
       <c r="Q10" s="23"/>
     </row>
-    <row r="11" ht="90.2" customHeight="true">
+    <row r="11" ht="96.05" customHeight="true">
       <c r="A11" s="0"/>
       <c r="B11" s="21" t="inlineStr">
         <is>
@@ -3887,7 +3887,7 @@
       </c>
       <c r="Q11" s="24"/>
     </row>
-    <row r="12" ht="90.2" customHeight="true">
+    <row r="12" ht="96.05" customHeight="true">
       <c r="A12" s="0"/>
       <c r="B12" s="21"/>
       <c r="C12" s="22"/>
@@ -3928,7 +3928,7 @@
       </c>
       <c r="Q12" s="22"/>
     </row>
-    <row r="13" ht="90.2" customHeight="true">
+    <row r="13" ht="96.05" customHeight="true">
       <c r="A13" s="0"/>
       <c r="B13" s="21" t="inlineStr">
         <is>
@@ -3971,7 +3971,7 @@
       </c>
       <c r="Q13" s="23"/>
     </row>
-    <row r="14" ht="90.2" customHeight="true">
+    <row r="14" ht="96.05" customHeight="true">
       <c r="A14" s="0"/>
       <c r="B14" s="21"/>
       <c r="C14" s="24"/>
@@ -4034,6 +4034,6 @@
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" scale="66"/>
+  <pageSetup paperSize="9" orientation="portrait" scale="62"/>
 </worksheet>
 </file>